--- a/artfynd/A 59357-2025 artfynd.xlsx
+++ b/artfynd/A 59357-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5738,6 +5738,713 @@
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>131737161</v>
+      </c>
+      <c r="B50" t="n">
+        <v>5493</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Niptjärnbäcken Nordväst, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>667427</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7083460</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Björna</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>131739425</v>
+      </c>
+      <c r="B51" t="n">
+        <v>90851</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Björnmyran Öst, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>667453</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7083583</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Björna</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>131732789</v>
+      </c>
+      <c r="B52" t="n">
+        <v>93116</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Niptjärnbäcken Nordväst, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>667528</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7083260</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Björna</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>131734708</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79017</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Björnmyran Öst, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>667488</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7083563</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Björna</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>131732778</v>
+      </c>
+      <c r="B54" t="n">
+        <v>93116</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Niptjärnbäcken Väst, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>667472</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7083479</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Björna</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>131734697</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79017</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Björnmyran Öst, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>667400</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7083548</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Björna</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>131734707</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79017</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Niptjärnbäcken Nordväst, Ång</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>667538</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7083252</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Björna</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59357-2025 artfynd.xlsx
+++ b/artfynd/A 59357-2025 artfynd.xlsx
@@ -6043,45 +6043,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131734708</v>
+        <v>131732778</v>
       </c>
       <c r="B53" t="n">
-        <v>79017</v>
+        <v>93116</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Björnmyran Öst, Ång</t>
+          <t>Niptjärnbäcken Väst, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>667488</v>
+        <v>667472</v>
       </c>
       <c r="R53" t="n">
-        <v>7083563</v>
+        <v>7083479</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6108,12 +6108,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Tomas Rask</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6144,45 +6144,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131732778</v>
+        <v>131734708</v>
       </c>
       <c r="B54" t="n">
-        <v>93116</v>
+        <v>79017</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Niptjärnbäcken Väst, Ång</t>
+          <t>Björnmyran Öst, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>667472</v>
+        <v>667488</v>
       </c>
       <c r="R54" t="n">
-        <v>7083479</v>
+        <v>7083563</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">

--- a/artfynd/A 59357-2025 artfynd.xlsx
+++ b/artfynd/A 59357-2025 artfynd.xlsx
@@ -5740,10 +5740,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131737161</v>
+        <v>131739425</v>
       </c>
       <c r="B50" t="n">
-        <v>5493</v>
+        <v>90852</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5751,34 +5751,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>101410</v>
+        <v>1962</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Niptjärnbäcken Nordväst, Ång</t>
+          <t>Björnmyran Öst, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>667427</v>
+        <v>667453</v>
       </c>
       <c r="R50" t="n">
-        <v>7083460</v>
+        <v>7083583</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5805,12 +5805,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Tomas Rask</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5841,10 +5841,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131739425</v>
+        <v>131737161</v>
       </c>
       <c r="B51" t="n">
-        <v>90851</v>
+        <v>5494</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5852,34 +5852,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1962</v>
+        <v>101410</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Björnmyran Öst, Ång</t>
+          <t>Niptjärnbäcken Nordväst, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>667453</v>
+        <v>667427</v>
       </c>
       <c r="R51" t="n">
-        <v>7083583</v>
+        <v>7083460</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5906,12 +5906,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5945,7 +5945,7 @@
         <v>131732789</v>
       </c>
       <c r="B52" t="n">
-        <v>93116</v>
+        <v>93117</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6043,45 +6043,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131732778</v>
+        <v>131734708</v>
       </c>
       <c r="B53" t="n">
-        <v>93116</v>
+        <v>79018</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Niptjärnbäcken Väst, Ång</t>
+          <t>Björnmyran Öst, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>667472</v>
+        <v>667488</v>
       </c>
       <c r="R53" t="n">
-        <v>7083479</v>
+        <v>7083563</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6108,12 +6108,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6144,45 +6144,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131734708</v>
+        <v>131732778</v>
       </c>
       <c r="B54" t="n">
-        <v>79017</v>
+        <v>93117</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Björnmyran Öst, Ång</t>
+          <t>Niptjärnbäcken Väst, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>667488</v>
+        <v>667472</v>
       </c>
       <c r="R54" t="n">
-        <v>7083563</v>
+        <v>7083479</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Tomas Rask</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6248,7 +6248,7 @@
         <v>131734697</v>
       </c>
       <c r="B55" t="n">
-        <v>79017</v>
+        <v>79018</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>131734707</v>
       </c>
       <c r="B56" t="n">
-        <v>79017</v>
+        <v>79018</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 59357-2025 artfynd.xlsx
+++ b/artfynd/A 59357-2025 artfynd.xlsx
@@ -5740,10 +5740,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131739425</v>
+        <v>131737161</v>
       </c>
       <c r="B50" t="n">
-        <v>90852</v>
+        <v>5494</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5751,34 +5751,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1962</v>
+        <v>101410</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Björnmyran Öst, Ång</t>
+          <t>Niptjärnbäcken Nordväst, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>667453</v>
+        <v>667427</v>
       </c>
       <c r="R50" t="n">
-        <v>7083583</v>
+        <v>7083460</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5805,12 +5805,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5841,10 +5841,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131737161</v>
+        <v>131739425</v>
       </c>
       <c r="B51" t="n">
-        <v>5494</v>
+        <v>90855</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5852,34 +5852,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>101410</v>
+        <v>1962</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Niptjärnbäcken Nordväst, Ång</t>
+          <t>Björnmyran Öst, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>667427</v>
+        <v>667453</v>
       </c>
       <c r="R51" t="n">
-        <v>7083460</v>
+        <v>7083583</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5906,12 +5906,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Tomas Rask</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5945,7 +5945,7 @@
         <v>131732789</v>
       </c>
       <c r="B52" t="n">
-        <v>93117</v>
+        <v>93120</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6043,45 +6043,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131734708</v>
+        <v>131732778</v>
       </c>
       <c r="B53" t="n">
-        <v>79018</v>
+        <v>93120</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Björnmyran Öst, Ång</t>
+          <t>Niptjärnbäcken Väst, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>667488</v>
+        <v>667472</v>
       </c>
       <c r="R53" t="n">
-        <v>7083563</v>
+        <v>7083479</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6108,12 +6108,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Tomas Rask</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6144,45 +6144,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131732778</v>
+        <v>131734708</v>
       </c>
       <c r="B54" t="n">
-        <v>93117</v>
+        <v>79021</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Niptjärnbäcken Väst, Ång</t>
+          <t>Björnmyran Öst, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>667472</v>
+        <v>667488</v>
       </c>
       <c r="R54" t="n">
-        <v>7083479</v>
+        <v>7083563</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6248,7 +6248,7 @@
         <v>131734697</v>
       </c>
       <c r="B55" t="n">
-        <v>79018</v>
+        <v>79021</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>131734707</v>
       </c>
       <c r="B56" t="n">
-        <v>79018</v>
+        <v>79021</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 59357-2025 artfynd.xlsx
+++ b/artfynd/A 59357-2025 artfynd.xlsx
@@ -6043,45 +6043,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131732778</v>
+        <v>131734708</v>
       </c>
       <c r="B53" t="n">
-        <v>93120</v>
+        <v>79021</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Niptjärnbäcken Väst, Ång</t>
+          <t>Björnmyran Öst, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>667472</v>
+        <v>667488</v>
       </c>
       <c r="R53" t="n">
-        <v>7083479</v>
+        <v>7083563</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6108,12 +6108,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6144,45 +6144,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131734708</v>
+        <v>131732778</v>
       </c>
       <c r="B54" t="n">
-        <v>79021</v>
+        <v>93120</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Björnmyran Öst, Ång</t>
+          <t>Niptjärnbäcken Väst, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>667488</v>
+        <v>667472</v>
       </c>
       <c r="R54" t="n">
-        <v>7083563</v>
+        <v>7083479</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Tomas Rask</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">

--- a/artfynd/A 59357-2025 artfynd.xlsx
+++ b/artfynd/A 59357-2025 artfynd.xlsx
@@ -6043,45 +6043,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131734708</v>
+        <v>131732778</v>
       </c>
       <c r="B53" t="n">
-        <v>79021</v>
+        <v>93120</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Björnmyran Öst, Ång</t>
+          <t>Niptjärnbäcken Väst, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>667488</v>
+        <v>667472</v>
       </c>
       <c r="R53" t="n">
-        <v>7083563</v>
+        <v>7083479</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6108,12 +6108,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Tomas Rask</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6144,45 +6144,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131732778</v>
+        <v>131734708</v>
       </c>
       <c r="B54" t="n">
-        <v>93120</v>
+        <v>79021</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Niptjärnbäcken Väst, Ång</t>
+          <t>Björnmyran Öst, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>667472</v>
+        <v>667488</v>
       </c>
       <c r="R54" t="n">
-        <v>7083479</v>
+        <v>7083563</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">

--- a/artfynd/A 59357-2025 artfynd.xlsx
+++ b/artfynd/A 59357-2025 artfynd.xlsx
@@ -5740,10 +5740,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131737161</v>
+        <v>131739425</v>
       </c>
       <c r="B50" t="n">
-        <v>5494</v>
+        <v>90861</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5751,34 +5751,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>101410</v>
+        <v>1962</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Niptjärnbäcken Nordväst, Ång</t>
+          <t>Björnmyran Öst, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>667427</v>
+        <v>667453</v>
       </c>
       <c r="R50" t="n">
-        <v>7083460</v>
+        <v>7083583</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5805,12 +5805,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Tomas Rask</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5841,10 +5841,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131739425</v>
+        <v>131737161</v>
       </c>
       <c r="B51" t="n">
-        <v>90855</v>
+        <v>5494</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5852,34 +5852,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1962</v>
+        <v>101410</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Björnmyran Öst, Ång</t>
+          <t>Niptjärnbäcken Nordväst, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>667453</v>
+        <v>667427</v>
       </c>
       <c r="R51" t="n">
-        <v>7083583</v>
+        <v>7083460</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5906,12 +5906,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5945,7 +5945,7 @@
         <v>131732789</v>
       </c>
       <c r="B52" t="n">
-        <v>93120</v>
+        <v>93126</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6043,45 +6043,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131734708</v>
+        <v>131732778</v>
       </c>
       <c r="B53" t="n">
-        <v>79021</v>
+        <v>93126</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Björnmyran Öst, Ång</t>
+          <t>Niptjärnbäcken Väst, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>667488</v>
+        <v>667472</v>
       </c>
       <c r="R53" t="n">
-        <v>7083563</v>
+        <v>7083479</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6108,12 +6108,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Tomas Rask</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6144,45 +6144,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131732778</v>
+        <v>131734708</v>
       </c>
       <c r="B54" t="n">
-        <v>93120</v>
+        <v>79023</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Niptjärnbäcken Väst, Ång</t>
+          <t>Björnmyran Öst, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>667472</v>
+        <v>667488</v>
       </c>
       <c r="R54" t="n">
-        <v>7083479</v>
+        <v>7083563</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6248,7 +6248,7 @@
         <v>131734697</v>
       </c>
       <c r="B55" t="n">
-        <v>79021</v>
+        <v>79023</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>131734707</v>
       </c>
       <c r="B56" t="n">
-        <v>79021</v>
+        <v>79023</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 59357-2025 artfynd.xlsx
+++ b/artfynd/A 59357-2025 artfynd.xlsx
@@ -5743,7 +5743,7 @@
         <v>131739425</v>
       </c>
       <c r="B50" t="n">
-        <v>90861</v>
+        <v>90864</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>131737161</v>
       </c>
       <c r="B51" t="n">
-        <v>5494</v>
+        <v>5495</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>131732789</v>
       </c>
       <c r="B52" t="n">
-        <v>93126</v>
+        <v>93129</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6043,45 +6043,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131732778</v>
+        <v>131734708</v>
       </c>
       <c r="B53" t="n">
-        <v>93126</v>
+        <v>79026</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Niptjärnbäcken Väst, Ång</t>
+          <t>Björnmyran Öst, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>667472</v>
+        <v>667488</v>
       </c>
       <c r="R53" t="n">
-        <v>7083479</v>
+        <v>7083563</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6108,12 +6108,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6144,45 +6144,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131734708</v>
+        <v>131732778</v>
       </c>
       <c r="B54" t="n">
-        <v>79023</v>
+        <v>93129</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Björnmyran Öst, Ång</t>
+          <t>Niptjärnbäcken Väst, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>667488</v>
+        <v>667472</v>
       </c>
       <c r="R54" t="n">
-        <v>7083563</v>
+        <v>7083479</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Tomas Rask</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6248,7 +6248,7 @@
         <v>131734697</v>
       </c>
       <c r="B55" t="n">
-        <v>79023</v>
+        <v>79026</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>131734707</v>
       </c>
       <c r="B56" t="n">
-        <v>79023</v>
+        <v>79026</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 59357-2025 artfynd.xlsx
+++ b/artfynd/A 59357-2025 artfynd.xlsx
@@ -5743,7 +5743,7 @@
         <v>131739425</v>
       </c>
       <c r="B50" t="n">
-        <v>90864</v>
+        <v>90869</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>131732789</v>
       </c>
       <c r="B52" t="n">
-        <v>93129</v>
+        <v>93134</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6043,45 +6043,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131734708</v>
+        <v>131732778</v>
       </c>
       <c r="B53" t="n">
-        <v>79026</v>
+        <v>93134</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Björnmyran Öst, Ång</t>
+          <t>Niptjärnbäcken Väst, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>667488</v>
+        <v>667472</v>
       </c>
       <c r="R53" t="n">
-        <v>7083563</v>
+        <v>7083479</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6108,12 +6108,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Tomas Rask</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6144,45 +6144,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131732778</v>
+        <v>131734708</v>
       </c>
       <c r="B54" t="n">
-        <v>93129</v>
+        <v>79031</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Niptjärnbäcken Väst, Ång</t>
+          <t>Björnmyran Öst, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>667472</v>
+        <v>667488</v>
       </c>
       <c r="R54" t="n">
-        <v>7083479</v>
+        <v>7083563</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6248,7 +6248,7 @@
         <v>131734697</v>
       </c>
       <c r="B55" t="n">
-        <v>79026</v>
+        <v>79031</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>131734707</v>
       </c>
       <c r="B56" t="n">
-        <v>79026</v>
+        <v>79031</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 59357-2025 artfynd.xlsx
+++ b/artfynd/A 59357-2025 artfynd.xlsx
@@ -5743,7 +5743,7 @@
         <v>131739425</v>
       </c>
       <c r="B50" t="n">
-        <v>90869</v>
+        <v>90871</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>131732789</v>
       </c>
       <c r="B52" t="n">
-        <v>93134</v>
+        <v>93136</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6043,45 +6043,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131732778</v>
+        <v>131734708</v>
       </c>
       <c r="B53" t="n">
-        <v>93134</v>
+        <v>79033</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Niptjärnbäcken Väst, Ång</t>
+          <t>Björnmyran Öst, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>667472</v>
+        <v>667488</v>
       </c>
       <c r="R53" t="n">
-        <v>7083479</v>
+        <v>7083563</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6108,12 +6108,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6144,45 +6144,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131734708</v>
+        <v>131732778</v>
       </c>
       <c r="B54" t="n">
-        <v>79031</v>
+        <v>93136</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Björnmyran Öst, Ång</t>
+          <t>Niptjärnbäcken Väst, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>667488</v>
+        <v>667472</v>
       </c>
       <c r="R54" t="n">
-        <v>7083563</v>
+        <v>7083479</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Tomas Rask</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6248,7 +6248,7 @@
         <v>131734697</v>
       </c>
       <c r="B55" t="n">
-        <v>79031</v>
+        <v>79033</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>131734707</v>
       </c>
       <c r="B56" t="n">
-        <v>79031</v>
+        <v>79033</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 59357-2025 artfynd.xlsx
+++ b/artfynd/A 59357-2025 artfynd.xlsx
@@ -6043,45 +6043,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131734708</v>
+        <v>131732778</v>
       </c>
       <c r="B53" t="n">
-        <v>79033</v>
+        <v>93136</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Björnmyran Öst, Ång</t>
+          <t>Niptjärnbäcken Väst, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>667488</v>
+        <v>667472</v>
       </c>
       <c r="R53" t="n">
-        <v>7083563</v>
+        <v>7083479</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6108,12 +6108,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Tomas Rask</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6144,45 +6144,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131732778</v>
+        <v>131734708</v>
       </c>
       <c r="B54" t="n">
-        <v>93136</v>
+        <v>79033</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Niptjärnbäcken Väst, Ång</t>
+          <t>Björnmyran Öst, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>667472</v>
+        <v>667488</v>
       </c>
       <c r="R54" t="n">
-        <v>7083479</v>
+        <v>7083563</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">

--- a/artfynd/A 59357-2025 artfynd.xlsx
+++ b/artfynd/A 59357-2025 artfynd.xlsx
@@ -5740,10 +5740,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131739425</v>
+        <v>131737161</v>
       </c>
       <c r="B50" t="n">
-        <v>90871</v>
+        <v>5495</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5751,34 +5751,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1962</v>
+        <v>101410</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Björnmyran Öst, Ång</t>
+          <t>Niptjärnbäcken Nordväst, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>667453</v>
+        <v>667427</v>
       </c>
       <c r="R50" t="n">
-        <v>7083583</v>
+        <v>7083460</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5805,12 +5805,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5841,10 +5841,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131737161</v>
+        <v>131739425</v>
       </c>
       <c r="B51" t="n">
-        <v>5495</v>
+        <v>90871</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5852,34 +5852,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>101410</v>
+        <v>1962</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Niptjärnbäcken Nordväst, Ång</t>
+          <t>Björnmyran Öst, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>667427</v>
+        <v>667453</v>
       </c>
       <c r="R51" t="n">
-        <v>7083460</v>
+        <v>7083583</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5906,12 +5906,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Tomas Rask</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">

--- a/artfynd/A 59357-2025 artfynd.xlsx
+++ b/artfynd/A 59357-2025 artfynd.xlsx
@@ -6043,45 +6043,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131732778</v>
+        <v>131734708</v>
       </c>
       <c r="B53" t="n">
-        <v>93136</v>
+        <v>79033</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Niptjärnbäcken Väst, Ång</t>
+          <t>Björnmyran Öst, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>667472</v>
+        <v>667488</v>
       </c>
       <c r="R53" t="n">
-        <v>7083479</v>
+        <v>7083563</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6108,12 +6108,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6144,45 +6144,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131734708</v>
+        <v>131732778</v>
       </c>
       <c r="B54" t="n">
-        <v>79033</v>
+        <v>93136</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Björnmyran Öst, Ång</t>
+          <t>Niptjärnbäcken Väst, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>667488</v>
+        <v>667472</v>
       </c>
       <c r="R54" t="n">
-        <v>7083563</v>
+        <v>7083479</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Tomas Rask</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">

--- a/artfynd/A 59357-2025 artfynd.xlsx
+++ b/artfynd/A 59357-2025 artfynd.xlsx
@@ -5740,10 +5740,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131737161</v>
+        <v>131739425</v>
       </c>
       <c r="B50" t="n">
-        <v>5495</v>
+        <v>90907</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5751,34 +5751,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>101410</v>
+        <v>1962</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Niptjärnbäcken Nordväst, Ång</t>
+          <t>Björnmyran Öst, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>667427</v>
+        <v>667453</v>
       </c>
       <c r="R50" t="n">
-        <v>7083460</v>
+        <v>7083583</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5805,12 +5805,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Tomas Rask</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5841,10 +5841,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131739425</v>
+        <v>131737161</v>
       </c>
       <c r="B51" t="n">
-        <v>90871</v>
+        <v>5495</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5852,34 +5852,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1962</v>
+        <v>101410</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Björnmyran Öst, Ång</t>
+          <t>Niptjärnbäcken Nordväst, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>667453</v>
+        <v>667427</v>
       </c>
       <c r="R51" t="n">
-        <v>7083583</v>
+        <v>7083460</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5906,12 +5906,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5945,7 +5945,7 @@
         <v>131732789</v>
       </c>
       <c r="B52" t="n">
-        <v>93136</v>
+        <v>93172</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>131734708</v>
       </c>
       <c r="B53" t="n">
-        <v>79033</v>
+        <v>79067</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>131732778</v>
       </c>
       <c r="B54" t="n">
-        <v>93136</v>
+        <v>93172</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>131734697</v>
       </c>
       <c r="B55" t="n">
-        <v>79033</v>
+        <v>79067</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>131734707</v>
       </c>
       <c r="B56" t="n">
-        <v>79033</v>
+        <v>79067</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 59357-2025 artfynd.xlsx
+++ b/artfynd/A 59357-2025 artfynd.xlsx
@@ -5844,7 +5844,7 @@
         <v>131739425</v>
       </c>
       <c r="B51" t="n">
-        <v>90912</v>
+        <v>90915</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>131732789</v>
       </c>
       <c r="B52" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>131732778</v>
       </c>
       <c r="B53" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>131734708</v>
       </c>
       <c r="B54" t="n">
-        <v>79072</v>
+        <v>79074</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>131734697</v>
       </c>
       <c r="B55" t="n">
-        <v>79072</v>
+        <v>79074</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>131734707</v>
       </c>
       <c r="B56" t="n">
-        <v>79072</v>
+        <v>79074</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 59357-2025 artfynd.xlsx
+++ b/artfynd/A 59357-2025 artfynd.xlsx
@@ -6043,45 +6043,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131732778</v>
+        <v>131734708</v>
       </c>
       <c r="B53" t="n">
-        <v>93180</v>
+        <v>79074</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Niptjärnbäcken Väst, Ång</t>
+          <t>Björnmyran Öst, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>667472</v>
+        <v>667488</v>
       </c>
       <c r="R53" t="n">
-        <v>7083479</v>
+        <v>7083563</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6108,12 +6108,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6144,45 +6144,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131734708</v>
+        <v>131732778</v>
       </c>
       <c r="B54" t="n">
-        <v>79074</v>
+        <v>93180</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Björnmyran Öst, Ång</t>
+          <t>Niptjärnbäcken Väst, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>667488</v>
+        <v>667472</v>
       </c>
       <c r="R54" t="n">
-        <v>7083563</v>
+        <v>7083479</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Tomas Rask</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">

--- a/artfynd/A 59357-2025 artfynd.xlsx
+++ b/artfynd/A 59357-2025 artfynd.xlsx
@@ -6043,45 +6043,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131734708</v>
+        <v>131732778</v>
       </c>
       <c r="B53" t="n">
-        <v>79074</v>
+        <v>93180</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Björnmyran Öst, Ång</t>
+          <t>Niptjärnbäcken Väst, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>667488</v>
+        <v>667472</v>
       </c>
       <c r="R53" t="n">
-        <v>7083563</v>
+        <v>7083479</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6108,12 +6108,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Tomas Rask</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6144,45 +6144,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131732778</v>
+        <v>131734708</v>
       </c>
       <c r="B54" t="n">
-        <v>93180</v>
+        <v>79074</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Niptjärnbäcken Väst, Ång</t>
+          <t>Björnmyran Öst, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>667472</v>
+        <v>667488</v>
       </c>
       <c r="R54" t="n">
-        <v>7083479</v>
+        <v>7083563</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">

--- a/artfynd/A 59357-2025 artfynd.xlsx
+++ b/artfynd/A 59357-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AZ61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901086</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111905138</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111905144</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111905145</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,6 +1191,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111905146</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111905141</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739425</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1485,6 +1525,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901087</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1582,6 +1627,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111905140</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1679,6 +1729,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111905142</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1776,6 +1831,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111905148</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1873,6 +1933,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111905152</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1970,6 +2035,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111905157</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2078,6 +2148,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111830798</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2175,6 +2250,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111905136</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2272,6 +2352,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111905159</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2380,6 +2465,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111831032</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2497,6 +2587,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111830925</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2605,6 +2700,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111831015</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2702,6 +2802,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901074</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2799,6 +2904,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901085</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2896,6 +3006,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111905135</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2993,6 +3108,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111905143</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3090,6 +3210,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111905147</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3187,6 +3312,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901077</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3284,6 +3414,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111905139</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3381,6 +3516,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67705359</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3478,6 +3618,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67705360</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3575,6 +3720,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901084</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3672,6 +3822,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111905149</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3773,6 +3928,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131732778</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3874,6 +4034,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131732787</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3973,6 +4138,11 @@
       <c r="AY34" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131732789</t>
         </is>
       </c>
     </row>
@@ -4086,6 +4256,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111830896</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4183,6 +4358,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67705357</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4280,6 +4460,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901071</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4377,6 +4562,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901076</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4474,6 +4664,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901078</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4571,6 +4766,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901082</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4668,6 +4868,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111905156</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4785,6 +4990,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111831007</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4882,6 +5092,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111905131</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4983,6 +5198,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737820</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5091,6 +5311,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111830850</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5208,6 +5433,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111830900</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5325,6 +5555,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111831022</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5422,6 +5657,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901072</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5519,6 +5759,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901075</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5625,6 +5870,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901080</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5722,6 +5972,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111905133</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5819,6 +6074,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111905150</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5916,6 +6176,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111905155</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6013,6 +6278,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111905158</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6114,6 +6384,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734697</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6215,6 +6490,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734707</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6316,6 +6596,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734708</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6413,6 +6698,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55717542</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6514,6 +6804,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737161</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6611,6 +6906,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55717537</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6706,8 +7006,75 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111905151</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>